--- a/evaluations/classification/classification_results_NEW_GLOBAL.xlsx
+++ b/evaluations/classification/classification_results_NEW_GLOBAL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,14 +538,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1019</v>
+        <v>4325</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         <v>256</v>
       </c>
       <c r="H2" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -591,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>35.7</v>
+        <v>54.59</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9512</v>
+        <v>0.8235</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9593</v>
+        <v>0.8764</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9589</v>
+        <v>0.8224</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -611,14 +611,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Giraffes</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>906</v>
+        <v>1019</v>
       </c>
       <c r="C3" t="n">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -664,16 +664,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>46.81</v>
+        <v>35.7</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7786</v>
+        <v>0.9512</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8295</v>
+        <v>0.9593</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7752</v>
+        <v>0.9589</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -684,14 +684,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HyenaID2022</t>
+          <t>Giraffes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2497</v>
+        <v>906</v>
       </c>
       <c r="C4" t="n">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -737,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>46.03</v>
+        <v>46.81</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7101</v>
+        <v>0.7786</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7899</v>
+        <v>0.8295</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6801</v>
+        <v>0.7752</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -757,14 +757,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>HyenaID2022</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1498</v>
+        <v>2497</v>
       </c>
       <c r="C5" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -810,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>38.6</v>
+        <v>46.03</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3671</v>
+        <v>0.7101</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.7899</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3169</v>
+        <v>0.6801</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -830,14 +830,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>655</v>
+        <v>1498</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -883,18 +883,91 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>655</v>
+      </c>
+      <c r="C7" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>256</v>
+      </c>
+      <c r="H7" t="n">
+        <v>128</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L7" t="n">
+        <v>50</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>40.19</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>

--- a/evaluations/classification/classification_results_NEW_GLOBAL.xlsx
+++ b/evaluations/classification/classification_results_NEW_GLOBAL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,22 +611,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CowDataset</t>
+          <t>ATRW</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1019</v>
+        <v>4325</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -638,11 +638,11 @@
         <v>128</v>
       </c>
       <c r="I3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>RANSAC</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -664,16 +664,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>35.7</v>
+        <v>0.97</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9512</v>
+        <v>0.6936</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9593</v>
+        <v>0.8386</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9589</v>
+        <v>0.6715</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -684,14 +684,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Giraffes</t>
+          <t>CowDataset</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>906</v>
+        <v>1019</v>
       </c>
       <c r="C4" t="n">
-        <v>170</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -737,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>46.81</v>
+        <v>35.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7786</v>
+        <v>0.9512</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8295</v>
+        <v>0.9593</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7752</v>
+        <v>0.9589</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -757,14 +757,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HyenaID2022</t>
+          <t>Giraffes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2497</v>
+        <v>906</v>
       </c>
       <c r="C5" t="n">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -810,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46.03</v>
+        <v>46.81</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7101</v>
+        <v>0.7786</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7899</v>
+        <v>0.8295</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6801</v>
+        <v>0.7752</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -830,14 +830,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NyalaData</t>
+          <t>HyenaID2022</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1498</v>
+        <v>2497</v>
       </c>
       <c r="C6" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -883,16 +883,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>38.6</v>
+        <v>46.03</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3671</v>
+        <v>0.7101</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.7899</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3169</v>
+        <v>0.6801</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -903,14 +903,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>655</v>
+        <v>1498</v>
       </c>
       <c r="C7" t="n">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -956,18 +956,91 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>655</v>
+      </c>
+      <c r="C8" t="n">
+        <v>43</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>256</v>
+      </c>
+      <c r="H8" t="n">
+        <v>128</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>40.19</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
